--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsChannelConstraint.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsChannelConstraint.xlsx
@@ -1180,11 +1180,11 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1">
       <formula1>ISNUMBER(E:I)</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576 C2:C1048576">
+      <formula1>ISTEXT(A2)</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:I1048576">
       <formula1>ISNUMBER(D2)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:C1048576">
-      <formula1>ISTEXT(A2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
